--- a/quality_surveys/009_sustainability_practice_integration_survey--quality_surveys.xlsx
+++ b/quality_surveys/009_sustainability_practice_integration_survey--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>operations_influence</t>
+          <t>operations_influence_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Operations Influence</t>
+          <t>Operations Influence 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>operations_influence_score</t>
+          <t>operations_influence_score_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Operations Influence Score</t>
+          <t>Operations Influence Score 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Environmental Practices</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Social Practices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Economic Practices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
